--- a/data/trending_integrated_20260910_14.xlsx
+++ b/data/trending_integrated_20260910_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4335</v>
+        <v>4265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+116.75%</t>
+          <t>+113.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>571</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="G2" t="n">
-        <v>166</v>
+        <v>571</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>856930000000</v>
+        <v>868887000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 급락 가능성 경고 및 단기 차익 실현 우려 제기. 주가 조작 의혹.</t>
+          <t>급등 후 변동성 확대, 개인 투자자 주의 촉구 및 목표가 논의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '급락', '주가 조작']</t>
+          <t>['스팩주', '변동성', '폭탄돌리기']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8300</v>
+        <v>8220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+45.36%</t>
+          <t>+43.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G3" t="n">
-        <v>1501</v>
+        <v>1525</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>68426000000</v>
+        <v>68752000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 폐암 학회 참여 및 다락손 관련 신규 임상 기대감. 글로벌 제약사 협력 및 대규모 재료.</t>
+          <t>폐암 학회 관련 글로벌 제약사 협력 및 임상 결과 발표 기대감, 재료 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['폐암 학회', '다락손', '신규 임상']</t>
+          <t>['폐암', '임상', 'FDA']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,7 +765,7 @@
         <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
         <v>103</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14660</v>
+        <v>14710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.13%</t>
+          <t>+24.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>163700000000</v>
+        <v>185019000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>우리기술, 원전주로서 미국 신규 건설 및 공매도 금지 관련 긍정적 전망. 2만 원 목표 및 양전 기대.</t>
+          <t>미국 신규 원전 건설 소식 기반 상승 기대감, 대장주 부각 및 공매도 관련 논쟁.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전주', '신규 건설', '공매도 금지']</t>
+          <t>['원전주', '신규건설', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14480</v>
+        <v>14640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+20.77%</t>
+          <t>+22.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="F6" t="n">
         <v>245</v>
       </c>
       <c r="G6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>293580000000</v>
+        <v>296525000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3575</v>
+        <v>3550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.57%</t>
+          <t>+17.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>26518000000</v>
+        <v>26735000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154500</v>
+        <v>12930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.96%</t>
+          <t>+12.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>317</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>758</v>
+        <v>54</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>383329000000</v>
+        <v>98266000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>단기 급등 후 개인 투자자들의 보유 비중 증가 및 프로그램 매수세 유입 관측.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['프로그램 매수', '단기 급등']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12790</v>
+        <v>154500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.93%</t>
+          <t>+11.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>413</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G9" t="n">
-        <v>53</v>
+        <v>1020</v>
       </c>
       <c r="H9" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>97963000000</v>
+        <v>386575000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['유가 폭등', '매집', '단기 차별화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
         <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="H10" t="n">
         <v>2.89</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 상승 추세 전망. 외국인 순매수세 확인.</t>
+          <t>미국 광통신 시장 강세 및 AI 관련주 부각, 외국인 순매수 전환으로 인한 상승 추세 예상.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1914</v>
+        <v>1919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.75%</t>
+          <t>+9.03%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
@@ -1438,7 +1438,7 @@
         <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>191337000000</v>
+        <v>192118000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 속 단기 급등락 반복, 전고점 돌파 기대감.</t>
+          <t>외인 매수세에도 불구하고 종가 하락, 기대감 속 변동성 장세 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['종가배팅', '주포', '거래량']</t>
+          <t>['종가배팅', '외인매수', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14250</v>
+        <v>14260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.53%</t>
+          <t>+8.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H12" t="n">
         <v>0.57</v>
@@ -1530,7 +1530,7 @@
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>118126000000</v>
+        <v>118620000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1575,39 +1575,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31100</v>
+        <v>2085</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="H13" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>20519000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,68 +1638,68 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
+          <t>새만금, 광주공항 등 테마 관련 기대감 속 개인 투자자 매수 지속, 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '개인 매수', '차익실현']</t>
+          <t>['테마주', '새만금', '수혜']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2070</v>
+        <v>31100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.70%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O14" t="n">
-        <v>20323000000</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,29 +1730,29 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기타법인 순매수 관측과 함께 테마주 수혜 및 반도체 관련 사업 기대감 존재.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인 매수', '테마주', '반도체']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3860</v>
+        <v>3890</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>140508000000</v>
+        <v>141691000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6730</v>
+        <v>6720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16" t="n">
         <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>15824000000</v>
+        <v>16010000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1862000</v>
+        <v>1852500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>+3.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>159</v>
+        <v>797</v>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="G17" t="n">
-        <v>419</v>
+        <v>2120</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -1990,7 +1990,7 @@
         <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>4428881000000</v>
+        <v>4556232000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수 전환 추세와 '네마녀의 날' 이후 상승 기대감 고조. 자사주 매입 완료 임박.</t>
+          <t>외인 매수 전환 기대감 속 연기금 리밸런싱 관련 논의, 기술적 반등 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인 매수', '네마녀의 날', '자사주 매입']</t>
+          <t>['외인매수', '리밸런싱', '기술적반등']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F18" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G18" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 미국 원전 8기 건설 '팀코리아' 참여 및 웨스팅하우스 지분 인수 기대감.</t>
+          <t>미국 원전 건설 '팀코리아' 관련 호재 및 웨스턴하우스 지분 인수 가능성, 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '팀코리아', '웨스팅하우스']</t>
+          <t>['원전주', '팀코리아', '호재']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F19" t="n">
         <v>123</v>
       </c>
       <c r="G19" t="n">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>개별 종목의 급락 및 단기 반등 예상, 그러나 투자자들의 혼란과 부정적 전망이 혼재.</t>
+          <t>단기 급락 후 개인 투자자 매수세 유입, 종목 패턴 분석 및 향후 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['일봉', '급락', '반등']</t>
+          <t>['단기급락', '개인매수', '급락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2311,39 +2311,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15640</v>
+        <v>248</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="E21" t="n">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F21" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>496</v>
+        <v>159</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15650</v>
+        <v>248</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
+          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '실적', '개미']</t>
+          <t>['상장폐지', '시가총액', '주가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>269000</v>
+        <v>15640</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>793</v>
+        <v>119</v>
       </c>
       <c r="F22" t="n">
-        <v>466</v>
+        <v>73</v>
       </c>
       <c r="G22" t="n">
-        <v>1430</v>
+        <v>502</v>
       </c>
       <c r="H22" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269500</v>
+        <v>15650</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2634013000000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,60 +2466,60 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 등 긍정적 뉴스에도 불구하고 정치적 언급 및 불확실한 기대감 혼재.</t>
+          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매수', '기대감']</t>
+          <t>['수주', '실적', '개미']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2125</v>
+        <v>269000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.62%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>797</v>
       </c>
       <c r="F23" t="n">
-        <v>47</v>
+        <v>468</v>
       </c>
       <c r="G23" t="n">
-        <v>179</v>
+        <v>1450</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>46.81</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2160</v>
+        <v>269500</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>46.85</v>
       </c>
       <c r="O23" t="n">
-        <v>6793000000</v>
+        <v>2743766000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,60 +2558,60 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>자사주 매수 및 배당 공시에 따른 기대감 존재, 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['자사주매수', '배당', '공시']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19150</v>
+        <v>2145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-4.11%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>420</v>
+        <v>184</v>
       </c>
       <c r="H24" t="n">
-        <v>10.64</v>
+        <v>4.91</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>19970</v>
+        <v>2160</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.85</v>
+        <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>96962000000</v>
+        <v>6901000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,68 +2650,68 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>대차해지 운동 집중, 미국 투자 및 원전 이슈 관련 기대감.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['대차해지', '미국 투자', '원전']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3650</v>
+        <v>19220</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G25" t="n">
-        <v>168</v>
+        <v>437</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
+        <v>10.64</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3890</v>
+        <v>19970</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>49588000000</v>
+        <v>101305000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,60 +2742,60 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>탈모 치료제 기대감 속 주가 변동성 확대, 차트 붕괴 및 나락 우려.</t>
+          <t>대차해지 운동 집중, 미국 투자 및 원전 이슈 관련 기대감.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['탈모', '신고가', '차트']</t>
+          <t>['대차해지', '미국 투자', '원전']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>513</v>
+        <v>3680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-15.49%</t>
+          <t>-5.40%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.38</v>
+        <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>64</v>
+        <v>172</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>1.54</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>607</v>
+        <v>3890</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>8512000000</v>
+        <v>49801000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>탈모 치료제 기대감 속 주가 변동성 확대, 차트 붕괴 및 나락 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['탈모', '신고가', '차트']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,46 +2856,46 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>150</v>
+        <v>505</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-18.92%</t>
+          <t>-16.80%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>185</v>
+        <v>607</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.08</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>788000000</v>
+        <v>8631000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['급등', '거래량', '회생']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,14 +2948,14 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>006380</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2963,31 +2963,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-39.52%</t>
+          <t>-18.92%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.32</v>
+        <v>-0.01</v>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F28" t="n">
         <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="H28" t="n">
-        <v>5.86</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>248</v>
+        <v>185</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.18</v>
+        <v>0.08</v>
       </c>
       <c r="O28" t="n">
-        <v>1011000000</v>
+        <v>788000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['상장폐지', '시가총액', '주가']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>006380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_14.xlsx
+++ b/data/trending_integrated_20260910_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4265</v>
+        <v>4060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+113.25%</t>
+          <t>+103.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G2" t="n">
-        <v>571</v>
+        <v>609</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>868887000000</v>
+        <v>879576000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 변동성 확대, 개인 투자자 주의 촉구 및 목표가 논의.</t>
+          <t>급등 후 폭락 가능성에 대한 경고와 함께 투자 주의 당부. 섣부른 투기 심리 경계.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '변동성', '폭탄돌리기']</t>
+          <t>['스펙주', '폭락', '투기']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8220</v>
+        <v>8140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+43.96%</t>
+          <t>+42.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>1525</v>
+        <v>1558</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>68752000000</v>
+        <v>69127000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>폐암 학회 관련 글로벌 제약사 협력 및 임상 결과 발표 기대감, 재료 기반 상승 전망.</t>
+          <t>폐암 학회 발표 및 글로벌 제약사와의 임상 협력 등 강력한 재료 기반 상승 전망. 임상 2상 결과 및 FDA 승인 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
         <v>103</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14710</v>
+        <v>14860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.56%</t>
+          <t>+25.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>775</v>
+        <v>849</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>185019000000</v>
+        <v>205446000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 소식 기반 상승 기대감, 대장주 부각 및 공매도 관련 논쟁.</t>
+          <t>미국 신규 원전 건설 관련 호재 및 대장주로서의 급등 기대감. 공매도 세력에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전주', '신규건설', '공매도']</t>
+          <t>['원전', '대장주', '급등 기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14640</v>
+        <v>14630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+22.10%</t>
+          <t>+22.02%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="F6" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G6" t="n">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>296525000000</v>
+        <v>300000000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>26735000000</v>
+        <v>26909000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12930</v>
+        <v>12910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.14%</t>
+          <t>+11.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H8" t="n">
         <v>4.37</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>98266000000</v>
+        <v>98604000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154500</v>
+        <v>153200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.96%</t>
+          <t>+11.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F9" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G9" t="n">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="H9" t="n">
         <v>15.65</v>
@@ -1254,7 +1254,7 @@
         <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>386575000000</v>
+        <v>392709000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
+          <t>유가 급등에 따른 주가 상승 기대감 존재. 프로그램 매수세 유입 및 JP모건의 대량 매수 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가 폭등', '매집', '단기 차별화']</t>
+          <t>['유가', '프로그램 매수', 'JP모건']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
         <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="H10" t="n">
         <v>2.89</v>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 강세 및 AI 관련주 부각, 외국인 순매수 전환으로 인한 상승 추세 예상.</t>
+          <t>미국 광통신 및 AI 관련주 강세에 따른 동반 상승 기대. 외국인 순매수세 전환 및 지수 동반 상승 가능성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.03%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
@@ -1438,7 +1438,7 @@
         <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>192118000000</v>
+        <v>192495000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외인 매수세에도 불구하고 종가 하락, 기대감 속 변동성 장세 전망.</t>
+          <t>외국인 순매수세 속 단기 급등락 후 횡보 예상. 주포의 개입 가능성과 함께 추가 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['종가배팅', '외인매수', '변동성']</t>
+          <t>['주포', '외국인', '횡보']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14260</v>
+        <v>14250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.61%</t>
+          <t>+8.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
         <v>143</v>
@@ -1530,7 +1530,7 @@
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>118620000000</v>
+        <v>119187000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F13" t="n">
         <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="H13" t="n">
         <v>0.85</v>
@@ -1622,7 +1622,7 @@
         <v>0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>20519000000</v>
+        <v>20575000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         <v>0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
         <v>12.31</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3890</v>
+        <v>3880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+6.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>141691000000</v>
+        <v>142306000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6720</v>
+        <v>1860000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+4.51%</t>
+          <t>+3.74%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.03</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>139</v>
+        <v>795</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>451</v>
       </c>
       <c r="G16" t="n">
-        <v>345</v>
+        <v>2180</v>
       </c>
       <c r="H16" t="n">
-        <v>15.68</v>
+        <v>50.67</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6430</v>
+        <v>1793000</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16.71</v>
+        <v>50.66</v>
       </c>
       <c r="O16" t="n">
-        <v>16010000000</v>
+        <v>4658426000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,20 +1914,20 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>한화 그룹주로서의 기대감 존재하나, 외국인 매도세 및 주가 부진 지속. 분사 이슈.</t>
+          <t>연기금 리밸런싱 효과 및 외국인 매수 전환 가능성 언급. 단기 조정 후 190만 이상 급등 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['한화', '외국인 매도', '분사']</t>
+          <t>['연기금', '외국인', '급등 전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1852500</v>
+        <v>6670</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.32%</t>
+          <t>+3.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-1.03</v>
       </c>
       <c r="E17" t="n">
-        <v>797</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>453</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>2120</v>
+        <v>339</v>
       </c>
       <c r="H17" t="n">
-        <v>50.67</v>
+        <v>15.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1793000</v>
+        <v>6430</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>50.66</v>
+        <v>16.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4556232000000</v>
+        <v>16372000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,20 +2006,20 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 매수 전환 기대감 속 연기금 리밸런싱 관련 논의, 기술적 반등 전망.</t>
+          <t>외국인 매도세 및 주가 하락에 대한 불만 제기. 로봇/반도체 섹터 일부 기대감은 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외인매수', '리밸런싱', '기술적반등']</t>
+          <t>['외국인', '주가 하락', '로봇 반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F18" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G18" t="n">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="F19" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G19" t="n">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>단기 급락 후 개인 투자자 매수세 유입, 종목 패턴 분석 및 향후 급락 가능성 경고.</t>
+          <t>급격한 주가 하락 및 매물 출회로 인한 투자 심리 위축. 명확한 근거 없는 기대감 속 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['단기급락', '개인매수', '급락']</t>
+          <t>['주가 하락', '매물', '투자 심리']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2311,11 +2311,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>248</v>
+        <v>269500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2323,27 +2323,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>795</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>459</v>
       </c>
       <c r="G21" t="n">
-        <v>159</v>
+        <v>1478</v>
       </c>
       <c r="H21" t="n">
-        <v>5.86</v>
+        <v>46.81</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>248</v>
+        <v>269500</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.18</v>
+        <v>46.85</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2797102000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2374,68 +2374,68 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
+          <t>자사주 매수 및 배당 공시에 따른 기대감 존재, 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['상장폐지', '시가총액', '주가']</t>
+          <t>['자사주매수', '배당', '공시']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15640</v>
+        <v>248</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>502</v>
+        <v>163</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15650</v>
+        <v>248</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
+          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수주', '실적', '개미']</t>
+          <t>['상장폐지', '시가총액', '주가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>269000</v>
+        <v>15640</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>797</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
-        <v>468</v>
+        <v>73</v>
       </c>
       <c r="G23" t="n">
-        <v>1450</v>
+        <v>502</v>
       </c>
       <c r="H23" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>269500</v>
+        <v>15650</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2743766000000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,29 +2558,29 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>자사주 매수 및 배당 공시에 따른 기대감 존재, 정치적 이슈 언급.</t>
+          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['자사주매수', '배당', '공시']</t>
+          <t>['수주', '실적', '개미']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H24" t="n">
         <v>4.91</v>
@@ -2634,7 +2634,7 @@
         <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>6901000000</v>
+        <v>6942000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19220</v>
+        <v>19400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.76%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F25" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G25" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>101305000000</v>
+        <v>108411000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차해지 운동 집중, 미국 투자 및 원전 이슈 관련 기대감.</t>
+          <t>대차해지 운동 참여 독려 및 원전 관련 호재 기대에도 불구하고 주가 하락세 지속. 국장 및 대우건설 자체의 부정적 인식.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '미국 투자', '원전']</t>
+          <t>['대차해지', '원전', '주가 하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3680</v>
+        <v>3665</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-5.40%</t>
+          <t>-5.78%</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>49801000000</v>
+        <v>50870000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2863,39 +2863,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>505</v>
+        <v>150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-16.80%</t>
+          <t>-18.92%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.38</v>
+        <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H27" t="n">
-        <v>2.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>0.08</v>
       </c>
       <c r="O27" t="n">
-        <v>8631000000</v>
+        <v>788000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,46 +2948,46 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>006380</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>150</v>
+        <v>465</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-18.92%</t>
+          <t>-23.39%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>185</v>
+        <v>607</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.08</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>788000000</v>
+        <v>9213000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['급등', '거래량', '회생']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>006380</t>
+          <t>033340</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_14.xlsx
+++ b/data/trending_integrated_20260910_14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4060</v>
+        <v>4040</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+103.00%</t>
+          <t>+102.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="F2" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G2" t="n">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>879576000000</v>
+        <v>894390000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 폭락 가능성에 대한 경고와 함께 투자 주의 당부. 섣부른 투기 심리 경계.</t>
+          <t>단기 급등 후 급락 가능성, 스펙주 특성상 투자 주의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스펙주', '폭락', '투기']</t>
+          <t>['스펙주', '급등', '급락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8140</v>
+        <v>8200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+42.56%</t>
+          <t>+43.61%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" t="n">
-        <v>1558</v>
+        <v>1590</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>69127000000</v>
+        <v>69491000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,13 +762,13 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14860</v>
+        <v>14730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+25.83%</t>
+          <t>+24.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>849</v>
+        <v>889</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>205446000000</v>
+        <v>216302000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 관련 호재 및 대장주로서의 급등 기대감. 공매도 세력에 대한 부정적 인식.</t>
+          <t>미국 신규원전 건설 관련, 2만 목표 대장주 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '대장주', '급등 기대']</t>
+          <t>['원전', '대장주', '기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14630</v>
+        <v>14590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+22.02%</t>
+          <t>+21.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F6" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="G6" t="n">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>300000000000</v>
+        <v>302452000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3550</v>
+        <v>3560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.74%</t>
+          <t>+18.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>26909000000</v>
+        <v>27028000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12910</v>
+        <v>12840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.97%</t>
+          <t>+11.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" t="n">
         <v>4.37</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>98604000000</v>
+        <v>98874000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F9" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G9" t="n">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="H9" t="n">
         <v>15.65</v>
@@ -1254,7 +1254,7 @@
         <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>392709000000</v>
+        <v>396269000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F10" t="n">
         <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="H10" t="n">
         <v>2.89</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI 관련주 강세에 따른 동반 상승 기대. 외국인 순매수세 전환 및 지수 동반 상승 가능성.</t>
+          <t>미국 광통신 및 반도체 강세, AI 관련주로 16000 돌파 목표.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외국인']</t>
+          <t>['광통신', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1920</v>
+        <v>1912</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.09%</t>
+          <t>+8.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
@@ -1438,7 +1438,7 @@
         <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>192495000000</v>
+        <v>193131000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 순매수세 속 단기 급등락 후 횡보 예상. 주포의 개입 가능성과 함께 추가 상승 기대감 존재.</t>
+          <t>외인 매수세 유입 속 단기 급등 기대감 있으나, 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '외국인', '횡보']</t>
+          <t>['외인', '급등', '기대감']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1530,7 +1530,7 @@
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>119187000000</v>
+        <v>119530000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1575,39 +1575,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2085</v>
+        <v>31100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.48%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O13" t="n">
-        <v>20575000000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,68 +1638,68 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>새만금, 광주공항 등 테마 관련 기대감 속 개인 투자자 매수 지속, 단기 급등 가능성.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['테마주', '새만금', '수혜']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31100</v>
+        <v>2070</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="H14" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>20713000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,29 +1730,29 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
+          <t>새만금 소식 및 반도체 건설 관련 테마주 언급, 그러나 자전거래 의혹.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인 매도', '개인 매수', '차익실현']</t>
+          <t>['테마주', '자전거래', '의혹']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3880</v>
+        <v>3895</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.59%</t>
+          <t>+7.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>142306000000</v>
+        <v>143170000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1860000</v>
+        <v>6860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+3.74%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>795</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>451</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>2180</v>
+        <v>342</v>
       </c>
       <c r="H16" t="n">
-        <v>50.67</v>
+        <v>15.68</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1793000</v>
+        <v>6430</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>50.66</v>
+        <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>4658426000000</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,20 +1914,20 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연기금 리밸런싱 효과 및 외국인 매수 전환 가능성 언급. 단기 조정 후 190만 이상 급등 전망.</t>
+          <t>외국인 매도세 및 주가 조작 의혹, 종목명 변경 후 기대감 낮음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['연기금', '외국인', '급등 전망']</t>
+          <t>['외국인 매도', '주가 조작', '의혹']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6670</v>
+        <v>7650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>+5.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.03</v>
+        <v>-0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="G17" t="n">
-        <v>339</v>
+        <v>696</v>
       </c>
       <c r="H17" t="n">
-        <v>15.68</v>
+        <v>11.62</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6430</v>
+        <v>7240</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16.71</v>
+        <v>11.71</v>
       </c>
       <c r="O17" t="n">
-        <v>16372000000</v>
+        <v>18713000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,20 +2006,20 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 주가 하락에 대한 불만 제기. 로봇/반도체 섹터 일부 기대감은 존재.</t>
+          <t>CP A2+ 부여 및 내년 신용등급 상향 전망, 정상화 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인', '주가 하락', '로봇 반도체']</t>
+          <t>['신용등급', 'CP', '정상화']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>91700</v>
+        <v>1865000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>+4.02%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>273</v>
+        <v>794</v>
       </c>
       <c r="F18" t="n">
-        <v>165</v>
+        <v>458</v>
       </c>
       <c r="G18" t="n">
-        <v>911</v>
+        <v>2285</v>
       </c>
       <c r="H18" t="n">
-        <v>23.65</v>
+        <v>50.67</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4783584000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,20 +2098,20 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 관련 호재 및 웨스턴하우스 지분 인수 가능성, 단기 급등 기대.</t>
+          <t>연기금 리밸런싱 및 외국인 매수 전환 가능성 언급, 500만 가 목표.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '팀코리아', '호재']</t>
+          <t>['리밸런싱', '외국인 매수', '목표']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,46 +2120,46 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30300</v>
+        <v>91700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F19" t="n">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="G19" t="n">
-        <v>491</v>
+        <v>924</v>
       </c>
       <c r="H19" t="n">
-        <v>0.33</v>
+        <v>23.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29750</v>
+        <v>89500</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2190,20 +2190,20 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 매물 출회로 인한 투자 심리 위축. 명확한 근거 없는 기대감 속 추가 하락 가능성 제기.</t>
+          <t>미국 원전 건설 '팀코리아' 관련 호재 및 웨스턴하우스 지분 인수 가능성, 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 하락', '매물', '투자 심리']</t>
+          <t>['원전주', '팀코리아', '호재']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,46 +2212,46 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23200</v>
+        <v>30300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>296</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="G20" t="n">
-        <v>96</v>
+        <v>514</v>
       </c>
       <c r="H20" t="n">
-        <v>7.54</v>
+        <v>0.33</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22900</v>
+        <v>29750</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>7.58</v>
+        <v>0.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2282,60 +2282,60 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자사주 매입 소각 가능성으로 인한 주가 상승 기대. 유통 물량 거래 활발.</t>
+          <t>단기 급락 이후 실망 매물 출회 및 프로그램 매매 관련 불만 제기. 일부 투자자는 추매를 긍정적으로 보나, 전반적인 투자 심리는 부정적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['급락', '매물', '추매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>269500</v>
+        <v>23200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>795</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>459</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>1478</v>
+        <v>101</v>
       </c>
       <c r="H21" t="n">
-        <v>46.81</v>
+        <v>7.54</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>269500</v>
+        <v>22900</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>46.85</v>
+        <v>7.58</v>
       </c>
       <c r="O21" t="n">
-        <v>2797102000000</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2374,68 +2374,68 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>자사주 매수 및 배당 공시에 따른 기대감 존재, 정치적 이슈 언급.</t>
+          <t>자사주 매입 소각 가능성으로 인한 주가 상승 기대. 유통 물량 거래 활발.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['자사주매수', '배당', '공시']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>248</v>
+        <v>269750</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>797</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>456</v>
       </c>
       <c r="G22" t="n">
-        <v>163</v>
+        <v>1497</v>
       </c>
       <c r="H22" t="n">
-        <v>5.86</v>
+        <v>46.81</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>248</v>
+        <v>269500</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6.18</v>
+        <v>46.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2896173000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,29 +2466,29 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
+          <t>15조 자사주 매수 발표로 호재 기대감 존재, 그러나 정치적 언급 다수.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['상장폐지', '시가총액', '주가']</t>
+          <t>['자사주 매수', '호재', '기대감']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2510,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F23" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G23" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
+          <t>LH 발주 호남 반도체 설계용역 수주 소식과 주차빌딩, 반도체 공장 건설 등 사업 확장 기대감. 하지만 개미 꼬시는 댓글과 주가 하락에 대한 불안감 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주', '실적', '개미']</t>
+          <t>['수주', '반도체', '건설']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H24" t="n">
         <v>4.91</v>
@@ -2634,7 +2634,7 @@
         <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>6942000000</v>
+        <v>7005000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19400</v>
+        <v>19530</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F25" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>441</v>
+        <v>500</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>108411000000</v>
+        <v>114424000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 원전 관련 호재 기대에도 불구하고 주가 하락세 지속. 국장 및 대우건설 자체의 부정적 인식.</t>
+          <t>대차해지 운동 독려 및 미국 투자 관련 언급, 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '원전', '주가 하락']</t>
+          <t>['대차해지', '운동', '기대']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>50870000000</v>
+        <v>51300000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-18.92%</t>
+          <t>-16.76%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" t="n">
         <v>0.07000000000000001</v>
@@ -2910,7 +2910,7 @@
         <v>0.08</v>
       </c>
       <c r="O27" t="n">
-        <v>788000000</v>
+        <v>815000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-23.39%</t>
+          <t>-24.55%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>9213000000</v>
+        <v>9525000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3041,6 +3041,98 @@
       <c r="Z28" t="inlineStr">
         <is>
           <t>033340</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>142</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-42.74%</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>92</v>
+      </c>
+      <c r="F29" t="n">
+        <v>47</v>
+      </c>
+      <c r="G29" t="n">
+        <v>173</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>248</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1058000000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>['상장폐지', '시가총액', '주가']</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>008290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_14.xlsx
+++ b/data/trending_integrated_20260910_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4040</v>
+        <v>4020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+102.00%</t>
+          <t>+101.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="F2" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G2" t="n">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>894390000000</v>
+        <v>902799000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>단기 급등 후 급락 가능성, 스펙주 특성상 투자 주의.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 638건 토론 포착</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스펙주', '급등', '급락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8200</v>
+        <v>8170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+43.61%</t>
+          <t>+43.08%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F3" t="n">
         <v>124</v>
       </c>
       <c r="G3" t="n">
-        <v>1590</v>
+        <v>1609</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>69491000000</v>
+        <v>69737000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>폐암 학회 발표 및 글로벌 제약사와의 임상 협력 등 강력한 재료 기반 상승 전망. 임상 2상 결과 및 FDA 승인 기대.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 314건 토론 포착</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['폐암', '임상', 'FDA']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
+        <v>122</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G4" t="n">
         <v>119</v>
-      </c>
-      <c r="F4" t="n">
-        <v>71</v>
-      </c>
-      <c r="G4" t="n">
-        <v>116</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>그래핀 등 신소재 관련 호재 언급 있으나, 주가 하락 의견과 혼재. 변동성 큼.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 122건 토론 포착</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '변동성']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14730</v>
+        <v>14700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.72%</t>
+          <t>+24.47%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>216302000000</v>
+        <v>222710000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14590</v>
+        <v>14360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+21.68%</t>
+          <t>+19.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F6" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G6" t="n">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>302452000000</v>
+        <v>306299000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>흥구석유, 중동 유가 급등 및 유조선 피격 관련 상승 기대. 단기 변동성 속 거래량 주목.</t>
+          <t>중동 유가 급등 및 전쟁 심화 관련하여 주가 상승 기대감 있으나, 변동성 큼.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유가 급등', '유조선 피격', '거래량']</t>
+          <t>['유가', '중동', '급등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3560</v>
+        <v>3550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.08%</t>
+          <t>+17.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>27028000000</v>
+        <v>27117000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12840</v>
+        <v>153500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.36%</t>
+          <t>+11.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>427</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>191</v>
       </c>
       <c r="G8" t="n">
-        <v>54</v>
+        <v>1041</v>
       </c>
       <c r="H8" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O8" t="n">
-        <v>98874000000</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 427건 토론 포착</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153200</v>
+        <v>12750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.01%</t>
+          <t>+10.58%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E9" t="n">
-        <v>428</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>1038</v>
+        <v>54</v>
       </c>
       <c r="H9" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>396269000000</v>
+        <v>99403000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 주가 상승 기대감 존재. 프로그램 매수세 유입 및 JP모건의 대량 매수 언급.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가', '프로그램 매수', 'JP모건']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,51 +1287,51 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14960</v>
+        <v>14340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.20%</t>
+          <t>+9.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.34</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>584</v>
+        <v>144</v>
       </c>
       <c r="H10" t="n">
-        <v>2.89</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13700</v>
+        <v>13130</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>119963000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 및 반도체 강세, AI 관련주로 16000 돌파 목표.</t>
+          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '반도체', 'AI']</t>
+          <t>['중동', '강관', '재무재표']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1912</v>
+        <v>1905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.64%</t>
+          <t>+8.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
@@ -1438,7 +1438,7 @@
         <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>193131000000</v>
+        <v>194506000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 속 단기 급등 기대감 있으나, 명확한 근거 부족.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 162건 토론 포착</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외인', '급등', '기대감']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14250</v>
+        <v>31100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.53%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.53</v>
+        <v>0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="H12" t="n">
-        <v>0.57</v>
+        <v>12.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13130</v>
+        <v>28750</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>12.14</v>
       </c>
       <c r="O12" t="n">
-        <v>119530000000</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['중동', '강관', '재무재표']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,46 +1568,46 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31100</v>
+        <v>14710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.37%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.17</v>
+        <v>1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>160</v>
+        <v>601</v>
       </c>
       <c r="H13" t="n">
-        <v>12.31</v>
+        <v>2.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28750</v>
+        <v>13700</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12.14</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>105988000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 164건 토론 포착</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '개인 매수', '차익실현']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.70%</t>
+          <t>+7.18%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H14" t="n">
         <v>0.85</v>
@@ -1714,7 +1714,7 @@
         <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>20713000000</v>
+        <v>20792000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3895</v>
+        <v>3890</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+7.01%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
         <v>231</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>143170000000</v>
+        <v>143911000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6860</v>
+        <v>7730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+6.69%</t>
+          <t>+6.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.03</v>
+        <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G16" t="n">
-        <v>342</v>
+        <v>765</v>
       </c>
       <c r="H16" t="n">
-        <v>15.68</v>
+        <v>11.62</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6430</v>
+        <v>7240</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16.71</v>
+        <v>11.71</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>21941000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 주가 조작 의혹, 종목명 변경 후 기대감 낮음.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 212건 토론 포착</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외국인 매도', '주가 조작', '의혹']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7650</v>
+        <v>6860</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+5.66%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.09</v>
+        <v>-1.03</v>
       </c>
       <c r="E17" t="n">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="F17" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>696</v>
+        <v>347</v>
       </c>
       <c r="H17" t="n">
-        <v>11.62</v>
+        <v>15.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7240</v>
+        <v>6430</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11.71</v>
+        <v>16.71</v>
       </c>
       <c r="O17" t="n">
-        <v>18713000000</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,20 +2006,20 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>CP A2+ 부여 및 내년 신용등급 상향 전망, 정상화 기대감.</t>
+          <t>외국인 매도세 및 주가 조작 의혹, 종목명 변경 후 기대감 낮음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신용등급', 'CP', '정상화']</t>
+          <t>['외국인 매도', '주가 조작', '의혹']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1865000</v>
+        <v>1869000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>+4.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F18" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G18" t="n">
-        <v>2285</v>
+        <v>2440</v>
       </c>
       <c r="H18" t="n">
         <v>50.67</v>
@@ -2082,7 +2082,7 @@
         <v>50.66</v>
       </c>
       <c r="O18" t="n">
-        <v>4783584000000</v>
+        <v>4947636000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>연기금 리밸런싱 및 외국인 매수 전환 가능성 언급, 500만 가 목표.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 795건 토론 포착</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['리밸런싱', '외국인 매수', '목표']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G19" t="n">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2234,13 +2234,13 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="F20" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G20" t="n">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="H20" t="n">
         <v>0.33</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>단기 급락 이후 실망 매물 출회 및 프로그램 매매 관련 불만 제기. 일부 투자자는 추매를 긍정적으로 보나, 전반적인 투자 심리는 부정적.</t>
+          <t>2대 주주 한국산업은행 언급에도 불구하고, 단기 급락 및 급등 예상 혼재. 탕후루 및 더본코리아 패턴 비교.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['급락', '매물', '추매']</t>
+          <t>['2대 주주', '패턴', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H21" t="n">
         <v>7.54</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>269750</v>
+        <v>269500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F22" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G22" t="n">
-        <v>1497</v>
+        <v>1535</v>
       </c>
       <c r="H22" t="n">
         <v>46.81</v>
@@ -2450,7 +2450,7 @@
         <v>46.85</v>
       </c>
       <c r="O22" t="n">
-        <v>2896173000000</v>
+        <v>2988698000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15조 자사주 매수 발표로 호재 기대감 존재, 그러나 정치적 언급 다수.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 795건 토론 포착</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매수', '호재', '기대감']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
         <v>76</v>
       </c>
       <c r="G23" t="n">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H24" t="n">
         <v>4.91</v>
@@ -2634,7 +2634,7 @@
         <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>7005000000</v>
+        <v>7077000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19530</v>
+        <v>19610</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>114424000000</v>
+        <v>123561000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려 및 미국 투자 관련 언급, 주가 상승 기대.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 139건 토론 포착</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '운동', '기대']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3665</v>
+        <v>3655</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-5.78%</t>
+          <t>-6.04%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F26" t="n">
         <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>51300000000</v>
+        <v>51698000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" t="n">
         <v>45</v>
@@ -2970,13 +2970,13 @@
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>9525000000</v>
+        <v>9968000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F29" t="n">
         <v>47</v>
       </c>
       <c r="G29" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_14.xlsx
+++ b/data/trending_integrated_20260910_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4020</v>
+        <v>3855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+101.00%</t>
+          <t>+92.75%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="F2" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G2" t="n">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>902799000000</v>
+        <v>914518000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 638건 토론 포착</t>
+          <t>급격한 주가 변동성 속 투자자들의 엇갈린 기대감 표출. 단기 차익 실현 후 재진입 금지 의견.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['스펙주', '변동성', '단기 차익']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8170</v>
+        <v>8160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+43.08%</t>
+          <t>+42.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F3" t="n">
         <v>124</v>
       </c>
       <c r="G3" t="n">
-        <v>1609</v>
+        <v>1655</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>69737000000</v>
+        <v>70102000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 314건 토론 포착</t>
+          <t>폐암학회 발표 및 글로벌 제약사와의 임상 협력 기대감 고조. 긍정적 데이터 발표 후 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['폐암학회', '임상 협력', '데이터 발표']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
         <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 122건 토론 포착</t>
+          <t>창사 이래 최대 호재 및 그래핀 신소재에 대한 기대감으로 주가 상승 가능성이 언급되나, 조정 및 폭락 가능성에 대한 언급도 있어 변동성이 예상됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['신소재', '그래핀', '호재']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14700</v>
+        <v>14600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.47%</t>
+          <t>+23.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>222710000000</v>
+        <v>228313000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 신규원전 건설 관련, 2만 목표 대장주 기대감.</t>
+          <t>미국 신규 원전 건설 소식에 따른 원전주 강세 전망. 대장주로서 2만원 돌파 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '대장주', '기대']</t>
+          <t>['원전주', '미국 신규 원전', '2만원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14360</v>
+        <v>14300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.77%</t>
+          <t>+19.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="F6" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G6" t="n">
-        <v>515</v>
+        <v>581</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>306299000000</v>
+        <v>309101000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 유가 급등 및 전쟁 심화 관련하여 주가 상승 기대감 있으나, 변동성 큼.</t>
+          <t>이란발 지정학적 리스크와 유가 급등 가능성 언급. 단기 급등 후 프로그램 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유가', '중동', '급등']</t>
+          <t>['유가', '지정학적 리스크', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,18 +1027,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3550</v>
+        <v>3560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.74%</t>
+          <t>+18.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>27117000000</v>
+        <v>27207000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F8" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G8" t="n">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>15.65</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 427건 토론 포착</t>
+          <t>유가 폭등으로 인한 기대감과 프로그램 매수세가 있으나, 원유 관련 주가 상승에 대한 의구심과 주가 하락 패턴에 대한 우려도 공존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['유가', '프로그램 매수', '원유']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12750</v>
+        <v>12700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.58%</t>
+          <t>+10.15%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1254,7 +1254,7 @@
         <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>99403000000</v>
+        <v>100254000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F10" t="n">
         <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
         <v>0.57</v>
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>119963000000</v>
+        <v>120335000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1391,39 +1391,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1905</v>
+        <v>2090</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.24%</t>
+          <t>+8.74%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1760</v>
+        <v>1922</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>194506000000</v>
+        <v>20886000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,20 +1454,20 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 162건 토론 포착</t>
+          <t>새만금 소식 및 반도체 건설 관련 테마주 언급, 그러나 자전거래 의혹.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['테마주', '자전거래', '의혹']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
         <v>0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
         <v>52</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14710</v>
+        <v>3930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+7.37%</t>
+          <t>+7.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>601</v>
+        <v>247</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13700</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>105988000000</v>
+        <v>146518000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 164건 토론 포착</t>
+          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,59 +1647,59 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['투기과열', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2060</v>
+        <v>1900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.18%</t>
+          <t>+7.95%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
+        <v>2.12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>1760</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.51</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>20792000000</v>
+        <v>195425000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>새만금 소식 및 반도체 건설 관련 테마주 언급, 그러나 자전거래 의혹.</t>
+          <t>외인 매수세에도 불구하고 종가 하락하며 기대감 저하. 그러나 일부 투자자는 반등 가능성 제시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테마주', '자전거래', '의혹']</t>
+          <t>['외인', '종가', '반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3890</v>
+        <v>14710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+7.37%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.62</v>
+        <v>1.34</v>
       </c>
       <c r="E15" t="n">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>231</v>
+        <v>645</v>
       </c>
       <c r="H15" t="n">
-        <v>1.57</v>
+        <v>2.89</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3640</v>
+        <v>13700</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.19</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>143911000000</v>
+        <v>108131000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,29 +1822,29 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
+          <t>미국 광통신 시장 강세 및 AI 관련주로 부각. 외국인 수급 개선과 함께 16000원 돌파 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '광통신']</t>
+          <t>['광통신', 'AI 관련주', '외국인 수급']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7730</v>
+        <v>7750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+6.77%</t>
+          <t>+7.04%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="H16" t="n">
         <v>11.62</v>
@@ -1898,7 +1898,7 @@
         <v>11.71</v>
       </c>
       <c r="O16" t="n">
-        <v>21941000000</v>
+        <v>25593000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 212건 토론 포착</t>
+          <t>CP 신용등급 상향 (A2+) 및 향후 더블A 등급 전망. 공매도와의 대결 구도 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['신용등급', 'CP', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-1.03</v>
       </c>
       <c r="E17" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F17" t="n">
         <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="H17" t="n">
         <v>15.68</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 주가 조작 의혹, 종목명 변경 후 기대감 낮음.</t>
+          <t>외국인 매도세와 회사 경영진에 대한 비판적 시각이 존재하며, 로봇/반도체 관련 기대감이 일부 있으나 전반적인 분위기는 부정적.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인 매도', '주가 조작', '의혹']</t>
+          <t>['외국인 매도', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1869000</v>
+        <v>1859000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="F18" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="G18" t="n">
-        <v>2440</v>
+        <v>2526</v>
       </c>
       <c r="H18" t="n">
         <v>50.67</v>
@@ -2082,7 +2082,7 @@
         <v>50.66</v>
       </c>
       <c r="O18" t="n">
-        <v>4947636000000</v>
+        <v>5079527000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 795건 토론 포착</t>
+          <t>ETF 리밸런싱 및 연기금 움직임 주목. 자사주 매입 종료 시점과 외국인 매수 전환 여부 관건.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ETF 리밸런싱', '연기금', '자사주 매입']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F19" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G19" t="n">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2234,13 +2234,13 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F20" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G20" t="n">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="H20" t="n">
         <v>0.33</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2대 주주 한국산업은행 언급에도 불구하고, 단기 급락 및 급등 예상 혼재. 탕후루 및 더본코리아 패턴 비교.</t>
+          <t>2대 주주 한국산업은행의 존재가 언급되었으나, 급격한 주가 하락과 프로그램 매매에 대한 불신이 존재하며 향후 하락 가능성에 대한 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['2대 주주', '패턴', '급락']</t>
+          <t>['한국산업은행', '프로그램 매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H21" t="n">
         <v>7.54</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>269500</v>
+        <v>15640</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>795</v>
+        <v>126</v>
       </c>
       <c r="F22" t="n">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>1535</v>
+        <v>516</v>
       </c>
       <c r="H22" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269500</v>
+        <v>15650</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2988698000000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,20 +2466,20 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 795건 토론 포착</t>
+          <t>반도체 공장 건설 등 수주 관련 뉴스가 있으나 주가에 미치는 영향은 미미하며, 종목에 대한 부정적인 시각과 기대감이 혼재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['수주', '반도체 공장', '건설']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15640</v>
+        <v>269250</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>795</v>
       </c>
       <c r="F23" t="n">
-        <v>76</v>
+        <v>444</v>
       </c>
       <c r="G23" t="n">
-        <v>514</v>
+        <v>1564</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>46.81</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15650</v>
+        <v>269500</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>46.85</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3072335000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,20 +2558,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>LH 발주 호남 반도체 설계용역 수주 소식과 주차빌딩, 반도체 공장 건설 등 사업 확장 기대감. 하지만 개미 꼬시는 댓글과 주가 하락에 대한 불안감 혼재.</t>
+          <t>자사주 매수 및 배당 관련 긍정적 뉴스 언급. 일부는 정치적 발언과 함께 27만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주', '반도체', '건설']</t>
+          <t>['자사주 매수', '배당', '27만원']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2135</v>
+        <v>19740</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.35</v>
+        <v>-0.21</v>
       </c>
       <c r="E24" t="n">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>198</v>
+        <v>545</v>
       </c>
       <c r="H24" t="n">
-        <v>4.91</v>
+        <v>10.64</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2160</v>
+        <v>19970</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.26</v>
+        <v>10.85</v>
       </c>
       <c r="O24" t="n">
-        <v>7077000000</v>
+        <v>132304000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,60 +2650,60 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>대차 해지 운동 참여 독려하며 주가 반등 기대감 고조. 미국 투자 관련 호재 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['대차 해지', '주가 반등', '미국 투자']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19610</v>
+        <v>2130</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="E25" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="F25" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>515</v>
+        <v>198</v>
       </c>
       <c r="H25" t="n">
-        <v>10.64</v>
+        <v>4.91</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>19970</v>
+        <v>2160</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.85</v>
+        <v>5.26</v>
       </c>
       <c r="O25" t="n">
-        <v>123561000000</v>
+        <v>7143000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 139건 토론 포착</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,20 +2751,20 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3655</v>
+        <v>3670</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.04%</t>
+          <t>-5.66%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>51698000000</v>
+        <v>51934000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-24.55%</t>
+          <t>-22.90%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>9968000000</v>
+        <v>10123000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F29" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>
